--- a/tests/CustomizeTestCases/PurchaseItemTestData.xlsx
+++ b/tests/CustomizeTestCases/PurchaseItemTestData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>Dataset</t>
   </si>
@@ -28,7 +28,13 @@
     <t>Password</t>
   </si>
   <si>
-    <t>ItemName</t>
+    <t>ItemName1</t>
+  </si>
+  <si>
+    <t>ItemName2</t>
+  </si>
+  <si>
+    <t>ItemName3</t>
   </si>
   <si>
     <t>NameOnCard</t>
@@ -61,7 +67,16 @@
     <t>Men Tshirt</t>
   </si>
   <si>
+    <t>Blue Top</t>
+  </si>
+  <si>
+    <t>Sleeveless Dress</t>
+  </si>
+  <si>
     <t>SigmaTestPro</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -117,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -125,20 +140,26 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -454,20 +475,22 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="11" width="15.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="13" width="15.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -489,10 +512,10 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
@@ -501,118 +524,152 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2"/>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="4">
+        <v>17</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="4">
         <v>912383278321</v>
       </c>
-      <c r="H2" s="4">
+      <c r="J2" s="4">
         <v>321</v>
       </c>
-      <c r="I2" s="4">
+      <c r="K2" s="4">
         <v>6</v>
       </c>
-      <c r="J2" s="4">
+      <c r="L2" s="4">
         <v>2032</v>
       </c>
-      <c r="K2" s="5"/>
+      <c r="M2" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="A3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>20</v>
+      </c>
       <c r="F3" s="1"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="7"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="6"/>
+      <c r="C4" s="9"/>
       <c r="D4" s="2"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="7"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="5"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="6"/>
+      <c r="C5" s="9"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="7"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
-      <c r="C6" s="6"/>
+      <c r="C6" s="9"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="7"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="6"/>
+      <c r="C7" s="9"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="7"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="C8" s="6"/>
+      <c r="C8" s="9"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="7"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tests/CustomizeTestCases/PurchaseItemTestData.xlsx
+++ b/tests/CustomizeTestCases/PurchaseItemTestData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Dataset</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>SigmaTestPro</t>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
@@ -84,7 +81,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,12 +92,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -132,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -140,7 +131,7 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
@@ -149,18 +140,6 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
@@ -168,7 +147,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -478,19 +457,19 @@
   <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="13" width="15.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="9" width="15.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -572,103 +551,93 @@
       <c r="M2" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
       <c r="M3" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="9"/>
+      <c r="C4" s="3"/>
       <c r="D4" s="2"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="5"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="9"/>
+      <c r="C5" s="3"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
-      <c r="C6" s="9"/>
+      <c r="C6" s="3"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="C7" s="9"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="C8" s="9"/>
+      <c r="C8" s="3"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
   </sheetData>
